--- a/data/input/Resumen Cotizador_GRUAS Y TRANSPORTE SAN LORENZO_2023_Final.xlsx
+++ b/data/input/Resumen Cotizador_GRUAS Y TRANSPORTE SAN LORENZO_2023_Final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\automatizacion-cotizaciones\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_D17B2D0C613F1091A6FCDAAA3B81C71A209F34B6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D1F0204-B238-48A0-BA82-D36DEA8E9D33}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3881EFEC-BD6A-441A-B176-525FF1F42DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9525" firstSheet="4" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ABRIL" sheetId="4" r:id="rId1"/>
@@ -48,9 +48,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2516,34 +2517,34 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="29">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$S/.-280A]\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="167" formatCode="&quot;S/.&quot;\ #,##0.00"/>
-    <numFmt numFmtId="168" formatCode="[$$-2C0A]\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="&quot;S/. &quot;#,##0.00"/>
-    <numFmt numFmtId="171" formatCode="_ &quot;S/.&quot;\ * #,##0.00_ ;_ &quot;S/.&quot;\ * \-#,##0.00_ ;_ &quot;S/.&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="172" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000000000000"/>
-    <numFmt numFmtId="174" formatCode="[$S/-280A]#,##0.00;[Red][$S/-280A]\-#,##0.00"/>
-    <numFmt numFmtId="175" formatCode="_ &quot;S/&quot;\ * #,##0.00_ ;_ &quot;S/&quot;\ * \-#,##0.00_ ;_ &quot;S/&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
-    <numFmt numFmtId="183" formatCode="_-[$€]* #,##0.00_-;\-[$€]* #,##0.00_-;_-[$€]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="184" formatCode="[$S/.-280A]\ #,##0.000"/>
-    <numFmt numFmtId="185" formatCode="_ &quot;S/.&quot;* #,##0.00_ ;_ &quot;S/.&quot;* \-#,##0.00_ ;_ &quot;S/.&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="186" formatCode="_(&quot;S/.&quot;\ * #,##0.00_);_(&quot;S/.&quot;\ * \(#,##0.00\);_(&quot;S/.&quot;\ * &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="187" formatCode="_ &quot;€&quot;* #,##0.00_ ;_ &quot;€&quot;* \-#,##0.00_ ;_ &quot;€&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="188" formatCode="#,##0.00&quot; € &quot;;\-#,##0.00&quot; € &quot;;&quot; -&quot;#&quot; € &quot;;@\ "/>
-    <numFmt numFmtId="189" formatCode="_ [$S/.-280A]\ * #,##0.00_ ;_ [$S/.-280A]\ * \-#,##0.00_ ;_ [$S/.-280A]\ * \-??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="[$S/.-280A]\ #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="168" formatCode="&quot;S/.&quot;\ #,##0.00"/>
+    <numFmt numFmtId="169" formatCode="[$$-2C0A]\ #,##0.00"/>
+    <numFmt numFmtId="170" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="&quot;S/. &quot;#,##0.00"/>
+    <numFmt numFmtId="172" formatCode="_ &quot;S/.&quot;\ * #,##0.00_ ;_ &quot;S/.&quot;\ * \-#,##0.00_ ;_ &quot;S/.&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="173" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0000000000000"/>
+    <numFmt numFmtId="175" formatCode="[$S/-280A]#,##0.00;[Red][$S/-280A]\-#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="_ &quot;S/&quot;\ * #,##0.00_ ;_ &quot;S/&quot;\ * \-#,##0.00_ ;_ &quot;S/&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="181" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="182" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="183" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
+    <numFmt numFmtId="184" formatCode="_-[$€]* #,##0.00_-;\-[$€]* #,##0.00_-;_-[$€]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="185" formatCode="[$S/.-280A]\ #,##0.000"/>
+    <numFmt numFmtId="186" formatCode="_ &quot;S/.&quot;* #,##0.00_ ;_ &quot;S/.&quot;* \-#,##0.00_ ;_ &quot;S/.&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="187" formatCode="_(&quot;S/.&quot;\ * #,##0.00_);_(&quot;S/.&quot;\ * \(#,##0.00\);_(&quot;S/.&quot;\ * &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="188" formatCode="_ &quot;€&quot;* #,##0.00_ ;_ &quot;€&quot;* \-#,##0.00_ ;_ &quot;€&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="189" formatCode="#,##0.00&quot; € &quot;;\-#,##0.00&quot; € &quot;;&quot; -&quot;#&quot; € &quot;;@\ "/>
+    <numFmt numFmtId="190" formatCode="_ [$S/.-280A]\ * #,##0.00_ ;_ [$S/.-280A]\ * \-#,##0.00_ ;_ [$S/.-280A]\ * \-??_ ;_ @_ "/>
   </numFmts>
   <fonts count="143">
     <font>
@@ -4830,26 +4831,26 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4989,18 +4990,18 @@
     <xf numFmtId="0" fontId="89" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="89" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="95" fillId="39" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="183" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="188" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="188" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="188" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="188" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -5075,15 +5076,15 @@
     </xf>
     <xf numFmtId="0" fontId="96" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5096,137 +5097,137 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="185" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="186" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="188" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="188" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="188" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="188" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="97" fillId="68" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -5483,20 +5484,20 @@
     </xf>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="76" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5527,10 +5528,10 @@
     <xf numFmtId="0" fontId="89" fillId="82" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="89" fillId="88" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="95" fillId="76" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="127" fillId="89" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="128" fillId="80" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
@@ -5543,32 +5544,32 @@
     <xf numFmtId="0" fontId="123" fillId="0" borderId="55" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="84" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="91" fillId="18" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="91" fillId="18" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="95" fillId="76" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="77" borderId="49" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="98" fillId="18" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="91" fillId="18" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="95" fillId="76" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="77" borderId="49" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="98" fillId="18" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5582,7 +5583,7 @@
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="95" fillId="76" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="77" borderId="49" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="98" fillId="18" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -5591,12 +5592,12 @@
     <xf numFmtId="0" fontId="1" fillId="77" borderId="49" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="98" fillId="18" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="190" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="134" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="635">
@@ -5669,71 +5670,71 @@
     <xf numFmtId="49" fontId="19" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="23" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="23" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="13" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="31" fillId="13" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="13" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="32" fillId="13" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="33" fillId="13" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="33" fillId="13" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="31" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="34" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="11" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="11" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="35" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="35" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="12" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="12" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="34" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="22" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="10" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="10" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="34" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="34" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="36" fillId="0" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5744,7 +5745,7 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5760,49 +5761,49 @@
     <xf numFmtId="49" fontId="23" fillId="14" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="31" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="32" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="33" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="33" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="31" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="11" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="11" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="35" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="35" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="10" borderId="21" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="10" borderId="21" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="34" fillId="10" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="34" fillId="10" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="46" fillId="0" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="46" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5823,43 +5824,43 @@
     <xf numFmtId="49" fontId="19" fillId="10" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="12" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="12" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="16" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="50" fillId="16" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="16" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="51" fillId="16" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="49" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="48" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="17" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="50" fillId="17" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="15" borderId="8" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="50" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="52" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="52" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="50" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="50" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="52" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="52" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="50" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5873,7 +5874,7 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5888,7 +5889,7 @@
     <xf numFmtId="3" fontId="23" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5897,7 +5898,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5909,7 +5910,7 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5927,70 +5928,70 @@
     <xf numFmtId="49" fontId="20" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="20" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="16" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="50" fillId="16" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="16" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="51" fillId="16" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="31" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="31" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="34" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="14" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="48" fillId="14" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="17" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="50" fillId="17" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="15" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="14" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="49" fillId="14" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="34" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="22" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="14" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="50" fillId="14" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="52" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="52" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6017,7 +6018,7 @@
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="23" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="14" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6026,7 +6027,7 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
@@ -6042,7 +6043,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6054,7 +6055,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6070,37 +6071,37 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="53" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="53" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="21" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="62" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="62" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="63" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="63" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="63" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="63" fillId="22" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="41" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="41" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="23" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="23" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6109,25 +6110,25 @@
     <xf numFmtId="0" fontId="55" fillId="24" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="10" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="10" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="15" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="15" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="58" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="58" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="64" fillId="7" borderId="16" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="64" fillId="7" borderId="16" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="10" borderId="16" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="10" borderId="16" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="16" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="10" borderId="16" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6154,34 +6155,34 @@
     <xf numFmtId="49" fontId="65" fillId="14" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="66" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="66" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="67" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="67" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="21" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="59" fillId="8" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="59" fillId="8" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="12" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="12" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="35" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="35" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="64" fillId="7" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="64" fillId="7" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -6194,7 +6195,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="18" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="11" fillId="18" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6203,112 +6204,112 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="70" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="70" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="70" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="70" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="71" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="71" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="72" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="72" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="21" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="62" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="62" fillId="13" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="62" fillId="8" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="62" fillId="8" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="73" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="73" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="70" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="70" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="70" fillId="11" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="70" fillId="11" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="12" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="74" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="74" fillId="10" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="70" fillId="12" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="70" fillId="12" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="74" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="74" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="70" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="70" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="75" fillId="7" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="75" fillId="7" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="70" fillId="10" borderId="16" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="70" fillId="10" borderId="16" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="70" fillId="12" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="70" fillId="12" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="16" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="44" fillId="16" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="72" fillId="16" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="72" fillId="16" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="62" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="62" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="73" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="73" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="53" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="17" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="44" fillId="17" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="15" borderId="8" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="76" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="76" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="70" fillId="12" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="70" fillId="12" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="73" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="73" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="70" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="70" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="75" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="75" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="44" fillId="14" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6323,8 +6324,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -6332,37 +6333,37 @@
     <xf numFmtId="49" fontId="20" fillId="14" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="55" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="55" fillId="16" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="66" fillId="16" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="66" fillId="16" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="67" fillId="16" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="67" fillId="16" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="59" fillId="22" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="59" fillId="22" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="20" fillId="26" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="20" fillId="26" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="57" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="57" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="15" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6371,22 +6372,22 @@
     <xf numFmtId="0" fontId="55" fillId="15" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="58" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="58" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="58" fillId="14" borderId="8" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="58" fillId="14" borderId="8" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="78" fillId="27" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="78" fillId="27" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="14" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="55" fillId="14" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="57" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="57" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -6396,46 +6397,46 @@
     <xf numFmtId="49" fontId="20" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="55" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="28" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="55" fillId="28" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="66" fillId="28" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="66" fillId="28" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="67" fillId="28" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="67" fillId="28" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="29" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="57" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="57" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="20" fillId="30" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="20" fillId="30" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="29" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="55" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="55" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="78" fillId="31" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="78" fillId="31" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="57" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="57" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="55" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
@@ -6443,19 +6444,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="41" fillId="10" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="41" fillId="10" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="40" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6476,7 +6477,7 @@
     <xf numFmtId="0" fontId="11" fillId="18" borderId="43" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6488,7 +6489,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="41" fillId="10" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="41" fillId="10" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="26" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6497,59 +6498,59 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="13" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="31" fillId="13" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="13" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="32" fillId="13" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="33" fillId="13" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="33" fillId="13" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="34" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="19" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="32" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="31" fillId="32" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="35" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="35" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="9" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="31" fillId="9" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="83" fillId="33" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="83" fillId="33" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="8" borderId="8" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="8" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="34" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="34" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6576,16 +6577,16 @@
     <xf numFmtId="0" fontId="18" fillId="10" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="18" borderId="45" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="11" fillId="18" borderId="45" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="18" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="11" fillId="18" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6647,13 +6648,13 @@
     <xf numFmtId="9" fontId="64" fillId="7" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="41" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="41" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="18" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6674,10 +6675,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="41" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="41" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -6693,58 +6694,58 @@
     <xf numFmtId="16" fontId="16" fillId="10" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="55" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="66" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="66" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="67" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="67" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="59" fillId="90" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="59" fillId="90" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="20" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="20" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="57" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="57" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="91" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="91" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="58" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="58" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="58" fillId="10" borderId="0" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="58" fillId="10" borderId="0" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="78" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="78" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="10" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="55" fillId="10" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="57" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="57" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="129" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6759,7 +6760,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="41" fillId="10" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="41" fillId="10" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="59" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6768,7 +6769,7 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6798,68 +6799,68 @@
     <xf numFmtId="0" fontId="20" fillId="92" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="34" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="55" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="14" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="55" fillId="14" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="93" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="55" fillId="93" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="56" fillId="93" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="56" fillId="93" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="93" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="93" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="24" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="57" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="57" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="94" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="55" fillId="94" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="95" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="12" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="12" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="2" borderId="8" xfId="550" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="55" fillId="2" borderId="8" xfId="550" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="56" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="548" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="452"/>
-    <xf numFmtId="167" fontId="133" fillId="27" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="133" fillId="27" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="58" xfId="548" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6871,7 +6872,7 @@
     <xf numFmtId="0" fontId="12" fillId="10" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="42" fillId="10" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="42" fillId="10" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6880,7 +6881,7 @@
     <xf numFmtId="0" fontId="43" fillId="10" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="10" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="10" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="6" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6904,43 +6905,43 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="66" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="66" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="67" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="67" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="11" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="11" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="10" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="12" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="12" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="64" fillId="7" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="64" fillId="7" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="10" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="10" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="10" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6992,10 +6993,10 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7004,22 +7005,22 @@
     <xf numFmtId="0" fontId="16" fillId="10" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="11" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7029,77 +7030,77 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="10" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="18" fillId="10" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="59" xfId="294" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="59" xfId="294" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="20" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="96" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="67" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="67" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="59" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="59" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="11" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="11" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="133" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="133" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="10" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="10" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="136" fillId="0" borderId="8" xfId="294" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="136" fillId="0" borderId="8" xfId="294" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="136" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="136" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -7107,7 +7108,301 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="294" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="59" xfId="503" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="14" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="14" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="14" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="55" fillId="0" borderId="36" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="55" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="55" fillId="0" borderId="38" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="10" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="10" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="3" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="19" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="19" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="10" borderId="4" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="10" borderId="8" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="18" borderId="26" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="10" borderId="26" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="26" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="23" xfId="548" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="24" xfId="548" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="55" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="55" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="55" fillId="10" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="26" xfId="146" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="4" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="8" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="8" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="59" xfId="503" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7118,300 +7413,6 @@
     </xf>
     <xf numFmtId="49" fontId="20" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="23" fillId="0" borderId="26" xfId="146" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="10" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="10" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="4" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="8" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="8" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="14" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="14" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="14" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="55" fillId="0" borderId="36" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="55" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="55" fillId="0" borderId="38" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="19" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="19" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="18" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="18" borderId="26" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="10" borderId="8" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="10" borderId="26" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="10" borderId="4" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="3" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="26" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="23" xfId="548" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="24" xfId="548" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="10" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="553">
@@ -19005,7 +19006,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="COLLAR"/>
@@ -19046,7 +19047,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="COLLAR"/>
@@ -19384,7 +19385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS20"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="20.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="20.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="256"/>
     <col min="2" max="2" width="11.5703125" style="256" bestFit="1" customWidth="1"/>
@@ -19426,36 +19427,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:123" ht="21" thickBot="1">
-      <c r="B1" s="574" t="s">
+      <c r="B1" s="535" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="575"/>
-      <c r="D1" s="575"/>
-      <c r="E1" s="575"/>
-      <c r="F1" s="575"/>
-      <c r="G1" s="575"/>
-      <c r="H1" s="575"/>
-      <c r="I1" s="575"/>
-      <c r="J1" s="576"/>
-      <c r="L1" s="571" t="s">
+      <c r="C1" s="536"/>
+      <c r="D1" s="536"/>
+      <c r="E1" s="536"/>
+      <c r="F1" s="536"/>
+      <c r="G1" s="536"/>
+      <c r="H1" s="536"/>
+      <c r="I1" s="536"/>
+      <c r="J1" s="537"/>
+      <c r="L1" s="538" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="572"/>
-      <c r="N1" s="572"/>
-      <c r="O1" s="572"/>
-      <c r="P1" s="572"/>
-      <c r="Q1" s="572"/>
-      <c r="R1" s="572"/>
-      <c r="S1" s="572"/>
-      <c r="T1" s="572"/>
-      <c r="U1" s="572"/>
-      <c r="V1" s="572"/>
-      <c r="W1" s="572"/>
-      <c r="X1" s="572"/>
-      <c r="Y1" s="572"/>
-      <c r="Z1" s="572"/>
-      <c r="AA1" s="572"/>
-      <c r="AB1" s="573"/>
+      <c r="M1" s="539"/>
+      <c r="N1" s="539"/>
+      <c r="O1" s="539"/>
+      <c r="P1" s="539"/>
+      <c r="Q1" s="539"/>
+      <c r="R1" s="539"/>
+      <c r="S1" s="539"/>
+      <c r="T1" s="539"/>
+      <c r="U1" s="539"/>
+      <c r="V1" s="539"/>
+      <c r="W1" s="539"/>
+      <c r="X1" s="539"/>
+      <c r="Y1" s="539"/>
+      <c r="Z1" s="539"/>
+      <c r="AA1" s="539"/>
+      <c r="AB1" s="540"/>
       <c r="AC1" s="354"/>
       <c r="AD1" s="354"/>
       <c r="AE1" s="354"/>
@@ -19661,10 +19662,10 @@
       <c r="B3" s="377">
         <v>1</v>
       </c>
-      <c r="C3" s="561" t="s">
+      <c r="C3" s="541" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="562"/>
+      <c r="D3" s="542"/>
       <c r="E3" s="375" t="s">
         <v>36</v>
       </c>
@@ -19692,11 +19693,11 @@
       <c r="L3" s="257" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="563" t="s">
+      <c r="M3" s="543" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="564"/>
-      <c r="O3" s="565"/>
+      <c r="N3" s="544"/>
+      <c r="O3" s="545"/>
       <c r="P3" s="258">
         <f>(((55*123)+(25*58)+(9*62)+(5*65))/160)/1.18</f>
         <v>48.188559322033896</v>
@@ -19773,36 +19774,36 @@
       </c>
     </row>
     <row r="4" spans="1:123" ht="21" thickBot="1">
-      <c r="B4" s="574" t="s">
+      <c r="B4" s="535" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="575"/>
-      <c r="D4" s="575"/>
-      <c r="E4" s="575"/>
-      <c r="F4" s="575"/>
-      <c r="G4" s="575"/>
-      <c r="H4" s="575"/>
-      <c r="I4" s="575"/>
-      <c r="J4" s="576"/>
-      <c r="L4" s="571" t="s">
+      <c r="C4" s="536"/>
+      <c r="D4" s="536"/>
+      <c r="E4" s="536"/>
+      <c r="F4" s="536"/>
+      <c r="G4" s="536"/>
+      <c r="H4" s="536"/>
+      <c r="I4" s="536"/>
+      <c r="J4" s="537"/>
+      <c r="L4" s="538" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="572"/>
-      <c r="N4" s="572"/>
-      <c r="O4" s="572"/>
-      <c r="P4" s="572"/>
-      <c r="Q4" s="572"/>
-      <c r="R4" s="572"/>
-      <c r="S4" s="572"/>
-      <c r="T4" s="572"/>
-      <c r="U4" s="572"/>
-      <c r="V4" s="572"/>
-      <c r="W4" s="572"/>
-      <c r="X4" s="572"/>
-      <c r="Y4" s="572"/>
-      <c r="Z4" s="572"/>
-      <c r="AA4" s="572"/>
-      <c r="AB4" s="573"/>
+      <c r="M4" s="539"/>
+      <c r="N4" s="539"/>
+      <c r="O4" s="539"/>
+      <c r="P4" s="539"/>
+      <c r="Q4" s="539"/>
+      <c r="R4" s="539"/>
+      <c r="S4" s="539"/>
+      <c r="T4" s="539"/>
+      <c r="U4" s="539"/>
+      <c r="V4" s="539"/>
+      <c r="W4" s="539"/>
+      <c r="X4" s="539"/>
+      <c r="Y4" s="539"/>
+      <c r="Z4" s="539"/>
+      <c r="AA4" s="539"/>
+      <c r="AB4" s="540"/>
       <c r="AC4" s="354"/>
       <c r="AD4" s="354"/>
       <c r="AE4" s="354"/>
@@ -20008,10 +20009,10 @@
       <c r="B6" s="377">
         <v>1</v>
       </c>
-      <c r="C6" s="561" t="s">
+      <c r="C6" s="541" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="562"/>
+      <c r="D6" s="542"/>
       <c r="E6" s="375" t="s">
         <v>36</v>
       </c>
@@ -20039,11 +20040,11 @@
       <c r="L6" s="257" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="563" t="s">
+      <c r="M6" s="543" t="s">
         <v>46</v>
       </c>
-      <c r="N6" s="564"/>
-      <c r="O6" s="565"/>
+      <c r="N6" s="544"/>
+      <c r="O6" s="545"/>
       <c r="P6" s="258">
         <f>55/1.18</f>
         <v>46.610169491525426</v>
@@ -20126,10 +20127,10 @@
       <c r="B7" s="374">
         <v>2</v>
       </c>
-      <c r="C7" s="569" t="s">
+      <c r="C7" s="546" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="570"/>
+      <c r="D7" s="547"/>
       <c r="E7" s="378" t="s">
         <v>36</v>
       </c>
@@ -20157,11 +20158,11 @@
       <c r="L7" s="279" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="566" t="s">
+      <c r="M7" s="548" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="567"/>
-      <c r="O7" s="568"/>
+      <c r="N7" s="549"/>
+      <c r="O7" s="550"/>
       <c r="P7" s="280">
         <v>65</v>
       </c>
@@ -20352,10 +20353,10 @@
       <c r="B8" s="377">
         <v>3</v>
       </c>
-      <c r="C8" s="561" t="s">
+      <c r="C8" s="541" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="562"/>
+      <c r="D8" s="542"/>
       <c r="E8" s="375" t="s">
         <v>36</v>
       </c>
@@ -20383,9 +20384,9 @@
       <c r="L8" s="257" t="s">
         <v>39</v>
       </c>
-      <c r="M8" s="563"/>
-      <c r="N8" s="564"/>
-      <c r="O8" s="565"/>
+      <c r="M8" s="543"/>
+      <c r="N8" s="544"/>
+      <c r="O8" s="545"/>
       <c r="P8" s="258">
         <f>78/1.18</f>
         <v>66.101694915254242</v>
@@ -20464,36 +20465,36 @@
       </c>
     </row>
     <row r="9" spans="1:123" ht="21" thickBot="1">
-      <c r="B9" s="574" t="s">
+      <c r="B9" s="535" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="575"/>
-      <c r="D9" s="575"/>
-      <c r="E9" s="575"/>
-      <c r="F9" s="575"/>
-      <c r="G9" s="575"/>
-      <c r="H9" s="575"/>
-      <c r="I9" s="575"/>
-      <c r="J9" s="576"/>
-      <c r="L9" s="571" t="s">
+      <c r="C9" s="536"/>
+      <c r="D9" s="536"/>
+      <c r="E9" s="536"/>
+      <c r="F9" s="536"/>
+      <c r="G9" s="536"/>
+      <c r="H9" s="536"/>
+      <c r="I9" s="536"/>
+      <c r="J9" s="537"/>
+      <c r="L9" s="538" t="s">
         <v>1</v>
       </c>
-      <c r="M9" s="572"/>
-      <c r="N9" s="572"/>
-      <c r="O9" s="572"/>
-      <c r="P9" s="572"/>
-      <c r="Q9" s="572"/>
-      <c r="R9" s="572"/>
-      <c r="S9" s="572"/>
-      <c r="T9" s="572"/>
-      <c r="U9" s="572"/>
-      <c r="V9" s="572"/>
-      <c r="W9" s="572"/>
-      <c r="X9" s="572"/>
-      <c r="Y9" s="572"/>
-      <c r="Z9" s="572"/>
-      <c r="AA9" s="572"/>
-      <c r="AB9" s="573"/>
+      <c r="M9" s="539"/>
+      <c r="N9" s="539"/>
+      <c r="O9" s="539"/>
+      <c r="P9" s="539"/>
+      <c r="Q9" s="539"/>
+      <c r="R9" s="539"/>
+      <c r="S9" s="539"/>
+      <c r="T9" s="539"/>
+      <c r="U9" s="539"/>
+      <c r="V9" s="539"/>
+      <c r="W9" s="539"/>
+      <c r="X9" s="539"/>
+      <c r="Y9" s="539"/>
+      <c r="Z9" s="539"/>
+      <c r="AA9" s="539"/>
+      <c r="AB9" s="540"/>
       <c r="AC9" s="354"/>
       <c r="AD9" s="354"/>
       <c r="AE9" s="354"/>
@@ -20699,10 +20700,10 @@
       <c r="B11" s="377">
         <v>1</v>
       </c>
-      <c r="C11" s="561" t="s">
+      <c r="C11" s="541" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="562"/>
+      <c r="D11" s="542"/>
       <c r="E11" s="375" t="s">
         <v>36</v>
       </c>
@@ -20727,11 +20728,11 @@
       <c r="L11" s="257" t="s">
         <v>39</v>
       </c>
-      <c r="M11" s="563" t="s">
+      <c r="M11" s="543" t="s">
         <v>46</v>
       </c>
-      <c r="N11" s="564"/>
-      <c r="O11" s="565"/>
+      <c r="N11" s="544"/>
+      <c r="O11" s="545"/>
       <c r="P11" s="258">
         <f>55/1.18</f>
         <v>46.610169491525426</v>
@@ -20810,36 +20811,36 @@
       </c>
     </row>
     <row r="12" spans="1:123" ht="21" thickBot="1">
-      <c r="B12" s="574" t="s">
+      <c r="B12" s="535" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="575"/>
-      <c r="D12" s="575"/>
-      <c r="E12" s="575"/>
-      <c r="F12" s="575"/>
-      <c r="G12" s="575"/>
-      <c r="H12" s="575"/>
-      <c r="I12" s="575"/>
-      <c r="J12" s="576"/>
-      <c r="L12" s="571" t="s">
+      <c r="C12" s="536"/>
+      <c r="D12" s="536"/>
+      <c r="E12" s="536"/>
+      <c r="F12" s="536"/>
+      <c r="G12" s="536"/>
+      <c r="H12" s="536"/>
+      <c r="I12" s="536"/>
+      <c r="J12" s="537"/>
+      <c r="L12" s="538" t="s">
         <v>1</v>
       </c>
-      <c r="M12" s="572"/>
-      <c r="N12" s="572"/>
-      <c r="O12" s="572"/>
-      <c r="P12" s="572"/>
-      <c r="Q12" s="572"/>
-      <c r="R12" s="572"/>
-      <c r="S12" s="572"/>
-      <c r="T12" s="572"/>
-      <c r="U12" s="572"/>
-      <c r="V12" s="572"/>
-      <c r="W12" s="572"/>
-      <c r="X12" s="572"/>
-      <c r="Y12" s="572"/>
-      <c r="Z12" s="572"/>
-      <c r="AA12" s="572"/>
-      <c r="AB12" s="573"/>
+      <c r="M12" s="539"/>
+      <c r="N12" s="539"/>
+      <c r="O12" s="539"/>
+      <c r="P12" s="539"/>
+      <c r="Q12" s="539"/>
+      <c r="R12" s="539"/>
+      <c r="S12" s="539"/>
+      <c r="T12" s="539"/>
+      <c r="U12" s="539"/>
+      <c r="V12" s="539"/>
+      <c r="W12" s="539"/>
+      <c r="X12" s="539"/>
+      <c r="Y12" s="539"/>
+      <c r="Z12" s="539"/>
+      <c r="AA12" s="539"/>
+      <c r="AB12" s="540"/>
       <c r="AC12" s="354"/>
       <c r="AD12" s="354"/>
       <c r="AE12" s="354"/>
@@ -21045,10 +21046,10 @@
       <c r="B14" s="377">
         <v>1</v>
       </c>
-      <c r="C14" s="561" t="s">
+      <c r="C14" s="541" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="562"/>
+      <c r="D14" s="542"/>
       <c r="E14" s="375" t="s">
         <v>36</v>
       </c>
@@ -21073,11 +21074,11 @@
       <c r="L14" s="257" t="s">
         <v>39</v>
       </c>
-      <c r="M14" s="563" t="s">
+      <c r="M14" s="543" t="s">
         <v>46</v>
       </c>
-      <c r="N14" s="564"/>
-      <c r="O14" s="565"/>
+      <c r="N14" s="544"/>
+      <c r="O14" s="545"/>
       <c r="P14" s="258">
         <f>55/1.18</f>
         <v>46.610169491525426</v>
@@ -21160,10 +21161,10 @@
       <c r="B15" s="374">
         <v>2</v>
       </c>
-      <c r="C15" s="569" t="s">
+      <c r="C15" s="546" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="570"/>
+      <c r="D15" s="547"/>
       <c r="E15" s="378" t="s">
         <v>36</v>
       </c>
@@ -21188,11 +21189,11 @@
       <c r="L15" s="279" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="566" t="s">
+      <c r="M15" s="548" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="567"/>
-      <c r="O15" s="568"/>
+      <c r="N15" s="549"/>
+      <c r="O15" s="550"/>
       <c r="P15" s="280">
         <v>65</v>
       </c>
@@ -21381,36 +21382,36 @@
     </row>
     <row r="16" spans="1:123" ht="21" thickBot="1"/>
     <row r="17" spans="1:123" ht="21" thickBot="1">
-      <c r="B17" s="574" t="s">
+      <c r="B17" s="535" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="575"/>
-      <c r="D17" s="575"/>
-      <c r="E17" s="575"/>
-      <c r="F17" s="575"/>
-      <c r="G17" s="575"/>
-      <c r="H17" s="575"/>
-      <c r="I17" s="575"/>
-      <c r="J17" s="576"/>
-      <c r="L17" s="571" t="s">
+      <c r="C17" s="536"/>
+      <c r="D17" s="536"/>
+      <c r="E17" s="536"/>
+      <c r="F17" s="536"/>
+      <c r="G17" s="536"/>
+      <c r="H17" s="536"/>
+      <c r="I17" s="536"/>
+      <c r="J17" s="537"/>
+      <c r="L17" s="538" t="s">
         <v>1</v>
       </c>
-      <c r="M17" s="572"/>
-      <c r="N17" s="572"/>
-      <c r="O17" s="572"/>
-      <c r="P17" s="572"/>
-      <c r="Q17" s="572"/>
-      <c r="R17" s="572"/>
-      <c r="S17" s="572"/>
-      <c r="T17" s="572"/>
-      <c r="U17" s="572"/>
-      <c r="V17" s="572"/>
-      <c r="W17" s="572"/>
-      <c r="X17" s="572"/>
-      <c r="Y17" s="572"/>
-      <c r="Z17" s="572"/>
-      <c r="AA17" s="572"/>
-      <c r="AB17" s="573"/>
+      <c r="M17" s="539"/>
+      <c r="N17" s="539"/>
+      <c r="O17" s="539"/>
+      <c r="P17" s="539"/>
+      <c r="Q17" s="539"/>
+      <c r="R17" s="539"/>
+      <c r="S17" s="539"/>
+      <c r="T17" s="539"/>
+      <c r="U17" s="539"/>
+      <c r="V17" s="539"/>
+      <c r="W17" s="539"/>
+      <c r="X17" s="539"/>
+      <c r="Y17" s="539"/>
+      <c r="Z17" s="539"/>
+      <c r="AA17" s="539"/>
+      <c r="AB17" s="540"/>
       <c r="AC17" s="354"/>
       <c r="AD17" s="354"/>
       <c r="AE17" s="354"/>
@@ -21616,10 +21617,10 @@
       <c r="B19" s="377">
         <v>1</v>
       </c>
-      <c r="C19" s="561" t="s">
+      <c r="C19" s="541" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="562"/>
+      <c r="D19" s="542"/>
       <c r="E19" s="375" t="s">
         <v>36</v>
       </c>
@@ -21644,11 +21645,11 @@
       <c r="L19" s="257" t="s">
         <v>39</v>
       </c>
-      <c r="M19" s="563" t="s">
+      <c r="M19" s="543" t="s">
         <v>46</v>
       </c>
-      <c r="N19" s="564"/>
-      <c r="O19" s="565"/>
+      <c r="N19" s="544"/>
+      <c r="O19" s="545"/>
       <c r="P19" s="258">
         <f>60/1.18</f>
         <v>50.847457627118644</v>
@@ -21731,10 +21732,10 @@
       <c r="B20" s="374">
         <v>2</v>
       </c>
-      <c r="C20" s="569" t="s">
+      <c r="C20" s="546" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="570"/>
+      <c r="D20" s="547"/>
       <c r="E20" s="378" t="s">
         <v>36</v>
       </c>
@@ -21759,11 +21760,11 @@
       <c r="L20" s="279" t="s">
         <v>61</v>
       </c>
-      <c r="M20" s="566" t="s">
+      <c r="M20" s="548" t="s">
         <v>51</v>
       </c>
-      <c r="N20" s="567"/>
-      <c r="O20" s="568"/>
+      <c r="N20" s="549"/>
+      <c r="O20" s="550"/>
       <c r="P20" s="280">
         <f>90/1.18</f>
         <v>76.271186440677965</v>
@@ -21953,6 +21954,20 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="L17:AB17"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="L12:AB12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="M15:O15"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="L1:AB1"/>
     <mergeCell ref="B9:J9"/>
@@ -21967,20 +21982,6 @@
     <mergeCell ref="M7:O7"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="M3:O3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="L17:AB17"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="L12:AB12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="M15:O15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -21990,7 +21991,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:BG40"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
     <col min="2" max="2" width="4.28515625" customWidth="1"/>
@@ -22029,39 +22030,39 @@
   <sheetData>
     <row r="2" spans="1:56" ht="15.75" thickBot="1"/>
     <row r="3" spans="1:56" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B3" s="614" t="s">
+      <c r="B3" s="551" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="615"/>
-      <c r="D3" s="615"/>
-      <c r="E3" s="615"/>
-      <c r="F3" s="615"/>
-      <c r="G3" s="615"/>
-      <c r="H3" s="615"/>
-      <c r="I3" s="615"/>
-      <c r="J3" s="616"/>
+      <c r="C3" s="552"/>
+      <c r="D3" s="552"/>
+      <c r="E3" s="552"/>
+      <c r="F3" s="552"/>
+      <c r="G3" s="552"/>
+      <c r="H3" s="552"/>
+      <c r="I3" s="552"/>
+      <c r="J3" s="553"/>
       <c r="K3" s="255" t="s">
         <v>63</v>
       </c>
-      <c r="L3" s="602" t="s">
+      <c r="L3" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="603"/>
-      <c r="N3" s="603"/>
-      <c r="O3" s="603"/>
-      <c r="P3" s="603"/>
-      <c r="Q3" s="603"/>
-      <c r="R3" s="603"/>
-      <c r="S3" s="603"/>
-      <c r="T3" s="603"/>
-      <c r="U3" s="603"/>
-      <c r="V3" s="603"/>
-      <c r="W3" s="603"/>
-      <c r="X3" s="603"/>
-      <c r="Y3" s="603"/>
-      <c r="Z3" s="603"/>
-      <c r="AA3" s="603"/>
-      <c r="AB3" s="604"/>
+      <c r="M3" s="555"/>
+      <c r="N3" s="555"/>
+      <c r="O3" s="555"/>
+      <c r="P3" s="555"/>
+      <c r="Q3" s="555"/>
+      <c r="R3" s="555"/>
+      <c r="S3" s="555"/>
+      <c r="T3" s="555"/>
+      <c r="U3" s="555"/>
+      <c r="V3" s="555"/>
+      <c r="W3" s="555"/>
+      <c r="X3" s="555"/>
+      <c r="Y3" s="555"/>
+      <c r="Z3" s="555"/>
+      <c r="AA3" s="555"/>
+      <c r="AB3" s="556"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
@@ -22180,13 +22181,13 @@
       <c r="AK4" s="16"/>
     </row>
     <row r="5" spans="1:56" s="50" customFormat="1" ht="409.5" customHeight="1" thickBot="1">
-      <c r="B5" s="577">
+      <c r="B5" s="582">
         <v>1</v>
       </c>
-      <c r="C5" s="596" t="s">
+      <c r="C5" s="581" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="596"/>
+      <c r="D5" s="581"/>
       <c r="E5" s="594"/>
       <c r="F5" s="592">
         <v>122</v>
@@ -22212,11 +22213,11 @@
       <c r="L5" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="M5" s="598" t="s">
+      <c r="M5" s="557" t="s">
         <v>69</v>
       </c>
-      <c r="N5" s="599"/>
-      <c r="O5" s="600"/>
+      <c r="N5" s="558"/>
+      <c r="O5" s="559"/>
       <c r="P5" s="216">
         <f>50/1.16</f>
         <v>43.103448275862071</v>
@@ -22305,9 +22306,9 @@
       <c r="AU5" s="75"/>
     </row>
     <row r="6" spans="1:56" ht="205.5" customHeight="1" thickBot="1">
-      <c r="B6" s="578"/>
-      <c r="C6" s="597"/>
-      <c r="D6" s="597"/>
+      <c r="B6" s="583"/>
+      <c r="C6" s="596"/>
+      <c r="D6" s="596"/>
       <c r="E6" s="595"/>
       <c r="F6" s="593"/>
       <c r="G6" s="591"/>
@@ -22329,37 +22330,37 @@
     </row>
     <row r="7" spans="1:56" ht="15.75" thickBot="1"/>
     <row r="8" spans="1:56" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B8" s="537" t="s">
+      <c r="B8" s="560" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="538"/>
-      <c r="D8" s="538"/>
-      <c r="E8" s="538"/>
-      <c r="F8" s="538"/>
-      <c r="G8" s="538"/>
-      <c r="H8" s="538"/>
-      <c r="I8" s="538"/>
-      <c r="J8" s="539"/>
+      <c r="C8" s="561"/>
+      <c r="D8" s="561"/>
+      <c r="E8" s="561"/>
+      <c r="F8" s="561"/>
+      <c r="G8" s="561"/>
+      <c r="H8" s="561"/>
+      <c r="I8" s="561"/>
+      <c r="J8" s="562"/>
       <c r="K8" s="141"/>
-      <c r="L8" s="602" t="s">
+      <c r="L8" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="M8" s="603"/>
-      <c r="N8" s="603"/>
-      <c r="O8" s="603"/>
-      <c r="P8" s="603"/>
-      <c r="Q8" s="603"/>
-      <c r="R8" s="603"/>
-      <c r="S8" s="603"/>
-      <c r="T8" s="603"/>
-      <c r="U8" s="603"/>
-      <c r="V8" s="603"/>
-      <c r="W8" s="603"/>
-      <c r="X8" s="603"/>
-      <c r="Y8" s="603"/>
-      <c r="Z8" s="603"/>
-      <c r="AA8" s="603"/>
-      <c r="AB8" s="604"/>
+      <c r="M8" s="555"/>
+      <c r="N8" s="555"/>
+      <c r="O8" s="555"/>
+      <c r="P8" s="555"/>
+      <c r="Q8" s="555"/>
+      <c r="R8" s="555"/>
+      <c r="S8" s="555"/>
+      <c r="T8" s="555"/>
+      <c r="U8" s="555"/>
+      <c r="V8" s="555"/>
+      <c r="W8" s="555"/>
+      <c r="X8" s="555"/>
+      <c r="Y8" s="555"/>
+      <c r="Z8" s="555"/>
+      <c r="AA8" s="555"/>
+      <c r="AB8" s="556"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
@@ -22484,10 +22485,10 @@
       <c r="B10" s="207">
         <v>1</v>
       </c>
-      <c r="C10" s="606" t="s">
+      <c r="C10" s="579" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="606"/>
+      <c r="D10" s="579"/>
       <c r="E10" s="208" t="s">
         <v>74</v>
       </c>
@@ -22508,14 +22509,14 @@
         <v>3975.9800000000005</v>
       </c>
       <c r="K10" s="165"/>
-      <c r="L10" s="580" t="s">
+      <c r="L10" s="573" t="s">
         <v>77</v>
       </c>
-      <c r="M10" s="581"/>
-      <c r="N10" s="582" t="s">
+      <c r="M10" s="574"/>
+      <c r="N10" s="575" t="s">
         <v>78</v>
       </c>
-      <c r="O10" s="583"/>
+      <c r="O10" s="576"/>
       <c r="P10" s="166">
         <f>26.9/1.16</f>
         <v>23.189655172413794</v>
@@ -22616,10 +22617,10 @@
       <c r="B11" s="188">
         <v>2</v>
       </c>
-      <c r="C11" s="579" t="s">
+      <c r="C11" s="572" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="579"/>
+      <c r="D11" s="572"/>
       <c r="E11" s="189" t="s">
         <v>74</v>
       </c>
@@ -22640,14 +22641,14 @@
         <v>5063</v>
       </c>
       <c r="K11" s="165"/>
-      <c r="L11" s="580" t="s">
+      <c r="L11" s="573" t="s">
         <v>81</v>
       </c>
-      <c r="M11" s="581"/>
-      <c r="N11" s="582" t="s">
+      <c r="M11" s="574"/>
+      <c r="N11" s="575" t="s">
         <v>82</v>
       </c>
-      <c r="O11" s="583"/>
+      <c r="O11" s="576"/>
       <c r="P11" s="166">
         <f>34.5/1.16</f>
         <v>29.741379310344829</v>
@@ -22747,10 +22748,10 @@
       <c r="B12" s="491">
         <v>3</v>
       </c>
-      <c r="C12" s="596" t="s">
+      <c r="C12" s="581" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="596"/>
+      <c r="D12" s="581"/>
       <c r="E12" s="206"/>
       <c r="F12" s="497">
         <v>120</v>
@@ -22761,7 +22762,7 @@
       <c r="H12" s="494" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="633" t="s">
+      <c r="I12" s="533" t="s">
         <v>83</v>
       </c>
       <c r="J12" s="492">
@@ -22772,11 +22773,11 @@
       <c r="L12" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="598" t="s">
+      <c r="M12" s="557" t="s">
         <v>84</v>
       </c>
-      <c r="N12" s="599"/>
-      <c r="O12" s="600"/>
+      <c r="N12" s="558"/>
+      <c r="O12" s="559"/>
       <c r="P12" s="216">
         <f>50/1.16</f>
         <v>43.103448275862071</v>
@@ -22869,10 +22870,10 @@
       <c r="B13" s="108">
         <v>4</v>
       </c>
-      <c r="C13" s="601" t="s">
+      <c r="C13" s="577" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="601"/>
+      <c r="D13" s="577"/>
       <c r="E13" s="109"/>
       <c r="F13" s="110">
         <v>120</v>
@@ -22883,7 +22884,7 @@
       <c r="H13" s="495" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="634" t="s">
+      <c r="I13" s="534" t="s">
         <v>86</v>
       </c>
       <c r="J13" s="493">
@@ -22897,10 +22898,10 @@
       <c r="L13" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="543" t="s">
+      <c r="M13" s="564" t="s">
         <v>88</v>
       </c>
-      <c r="N13" s="544"/>
+      <c r="N13" s="565"/>
       <c r="O13" s="81"/>
       <c r="P13" s="234">
         <f>58/1.18</f>
@@ -23014,37 +23015,37 @@
     </row>
     <row r="14" spans="1:56" ht="15.75" thickBot="1"/>
     <row r="15" spans="1:56" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B15" s="537" t="s">
+      <c r="B15" s="560" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="538"/>
-      <c r="D15" s="538"/>
-      <c r="E15" s="538"/>
-      <c r="F15" s="538"/>
-      <c r="G15" s="538"/>
-      <c r="H15" s="538"/>
-      <c r="I15" s="538"/>
-      <c r="J15" s="539"/>
+      <c r="C15" s="561"/>
+      <c r="D15" s="561"/>
+      <c r="E15" s="561"/>
+      <c r="F15" s="561"/>
+      <c r="G15" s="561"/>
+      <c r="H15" s="561"/>
+      <c r="I15" s="561"/>
+      <c r="J15" s="562"/>
       <c r="K15" s="141"/>
-      <c r="L15" s="602" t="s">
+      <c r="L15" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="M15" s="603"/>
-      <c r="N15" s="603"/>
-      <c r="O15" s="603"/>
-      <c r="P15" s="603"/>
-      <c r="Q15" s="603"/>
-      <c r="R15" s="603"/>
-      <c r="S15" s="603"/>
-      <c r="T15" s="603"/>
-      <c r="U15" s="603"/>
-      <c r="V15" s="603"/>
-      <c r="W15" s="603"/>
-      <c r="X15" s="603"/>
-      <c r="Y15" s="603"/>
-      <c r="Z15" s="603"/>
-      <c r="AA15" s="603"/>
-      <c r="AB15" s="604"/>
+      <c r="M15" s="555"/>
+      <c r="N15" s="555"/>
+      <c r="O15" s="555"/>
+      <c r="P15" s="555"/>
+      <c r="Q15" s="555"/>
+      <c r="R15" s="555"/>
+      <c r="S15" s="555"/>
+      <c r="T15" s="555"/>
+      <c r="U15" s="555"/>
+      <c r="V15" s="555"/>
+      <c r="W15" s="555"/>
+      <c r="X15" s="555"/>
+      <c r="Y15" s="555"/>
+      <c r="Z15" s="555"/>
+      <c r="AA15" s="555"/>
+      <c r="AB15" s="556"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
       <c r="AE15" s="1"/>
@@ -23167,10 +23168,10 @@
       <c r="B17" s="188">
         <v>1</v>
       </c>
-      <c r="C17" s="579" t="s">
+      <c r="C17" s="572" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="579"/>
+      <c r="D17" s="572"/>
       <c r="E17" s="189" t="s">
         <v>74</v>
       </c>
@@ -23191,14 +23192,14 @@
         <v>3853.98</v>
       </c>
       <c r="K17" s="165"/>
-      <c r="L17" s="580" t="s">
+      <c r="L17" s="573" t="s">
         <v>77</v>
       </c>
-      <c r="M17" s="581"/>
-      <c r="N17" s="582" t="s">
+      <c r="M17" s="574"/>
+      <c r="N17" s="575" t="s">
         <v>78</v>
       </c>
-      <c r="O17" s="583"/>
+      <c r="O17" s="576"/>
       <c r="P17" s="166">
         <f>26.5/1.16</f>
         <v>22.844827586206897</v>
@@ -23299,10 +23300,10 @@
       <c r="B18" s="188">
         <v>2</v>
       </c>
-      <c r="C18" s="579" t="s">
+      <c r="C18" s="572" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="579"/>
+      <c r="D18" s="572"/>
       <c r="E18" s="189" t="s">
         <v>74</v>
       </c>
@@ -23323,14 +23324,14 @@
         <v>4915.38</v>
       </c>
       <c r="K18" s="165"/>
-      <c r="L18" s="580" t="s">
+      <c r="L18" s="573" t="s">
         <v>81</v>
       </c>
-      <c r="M18" s="581"/>
-      <c r="N18" s="582" t="s">
+      <c r="M18" s="574"/>
+      <c r="N18" s="575" t="s">
         <v>82</v>
       </c>
-      <c r="O18" s="583"/>
+      <c r="O18" s="576"/>
       <c r="P18" s="166">
         <f>34/1.17</f>
         <v>29.059829059829063</v>
@@ -23430,10 +23431,10 @@
       <c r="B19" s="191">
         <v>1</v>
       </c>
-      <c r="C19" s="607" t="s">
+      <c r="C19" s="580" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="607"/>
+      <c r="D19" s="580"/>
       <c r="E19" s="192"/>
       <c r="F19" s="497">
         <v>120</v>
@@ -23453,11 +23454,11 @@
       <c r="L19" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="M19" s="598" t="s">
+      <c r="M19" s="557" t="s">
         <v>95</v>
       </c>
-      <c r="N19" s="599"/>
-      <c r="O19" s="600"/>
+      <c r="N19" s="558"/>
+      <c r="O19" s="559"/>
       <c r="P19" s="58">
         <f>48.5/1.17</f>
         <v>41.452991452991455</v>
@@ -23550,10 +23551,10 @@
       <c r="B20" s="158">
         <v>4</v>
       </c>
-      <c r="C20" s="605" t="s">
+      <c r="C20" s="563" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="605"/>
+      <c r="D20" s="563"/>
       <c r="E20" s="77"/>
       <c r="F20" s="78">
         <v>120</v>
@@ -23578,10 +23579,10 @@
       <c r="L20" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="M20" s="543" t="s">
+      <c r="M20" s="564" t="s">
         <v>88</v>
       </c>
-      <c r="N20" s="544"/>
+      <c r="N20" s="565"/>
       <c r="O20" s="81"/>
       <c r="P20" s="82">
         <v>46</v>
@@ -23694,39 +23695,39 @@
     </row>
     <row r="21" spans="1:59" ht="15.75" thickBot="1"/>
     <row r="22" spans="1:59" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B22" s="537" t="s">
+      <c r="B22" s="560" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="538"/>
-      <c r="D22" s="538"/>
-      <c r="E22" s="538"/>
-      <c r="F22" s="538"/>
-      <c r="G22" s="538"/>
-      <c r="H22" s="538"/>
-      <c r="I22" s="538"/>
-      <c r="J22" s="539"/>
+      <c r="C22" s="561"/>
+      <c r="D22" s="561"/>
+      <c r="E22" s="561"/>
+      <c r="F22" s="561"/>
+      <c r="G22" s="561"/>
+      <c r="H22" s="561"/>
+      <c r="I22" s="561"/>
+      <c r="J22" s="562"/>
       <c r="K22" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="L22" s="602" t="s">
+      <c r="L22" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="M22" s="603"/>
-      <c r="N22" s="603"/>
-      <c r="O22" s="603"/>
-      <c r="P22" s="603"/>
-      <c r="Q22" s="603"/>
-      <c r="R22" s="603"/>
-      <c r="S22" s="603"/>
-      <c r="T22" s="603"/>
-      <c r="U22" s="603"/>
-      <c r="V22" s="603"/>
-      <c r="W22" s="603"/>
-      <c r="X22" s="603"/>
-      <c r="Y22" s="603"/>
-      <c r="Z22" s="603"/>
-      <c r="AA22" s="603"/>
-      <c r="AB22" s="604"/>
+      <c r="M22" s="555"/>
+      <c r="N22" s="555"/>
+      <c r="O22" s="555"/>
+      <c r="P22" s="555"/>
+      <c r="Q22" s="555"/>
+      <c r="R22" s="555"/>
+      <c r="S22" s="555"/>
+      <c r="T22" s="555"/>
+      <c r="U22" s="555"/>
+      <c r="V22" s="555"/>
+      <c r="W22" s="555"/>
+      <c r="X22" s="555"/>
+      <c r="Y22" s="555"/>
+      <c r="Z22" s="555"/>
+      <c r="AA22" s="555"/>
+      <c r="AB22" s="556"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
       <c r="AE22" s="1"/>
@@ -23849,10 +23850,10 @@
       <c r="B24" s="153">
         <v>1</v>
       </c>
-      <c r="C24" s="617" t="s">
+      <c r="C24" s="566" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="617"/>
+      <c r="D24" s="566"/>
       <c r="E24" s="154"/>
       <c r="F24" s="161">
         <v>120</v>
@@ -23876,10 +23877,10 @@
       <c r="L24" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="M24" s="610" t="s">
+      <c r="M24" s="567" t="s">
         <v>103</v>
       </c>
-      <c r="N24" s="611"/>
+      <c r="N24" s="568"/>
       <c r="O24" s="25"/>
       <c r="P24" s="26">
         <v>8</v>
@@ -24008,10 +24009,10 @@
       <c r="B25" s="157">
         <v>2</v>
       </c>
-      <c r="C25" s="613" t="s">
+      <c r="C25" s="569" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="613"/>
+      <c r="D25" s="569"/>
       <c r="E25" s="52"/>
       <c r="F25" s="53">
         <v>120</v>
@@ -24036,10 +24037,10 @@
       <c r="L25" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="M25" s="608" t="s">
+      <c r="M25" s="570" t="s">
         <v>107</v>
       </c>
-      <c r="N25" s="609"/>
+      <c r="N25" s="571"/>
       <c r="P25" s="58">
         <f>38/1.17</f>
         <v>32.478632478632484</v>
@@ -24156,10 +24157,10 @@
       <c r="B26" s="158">
         <v>3</v>
       </c>
-      <c r="C26" s="605" t="s">
+      <c r="C26" s="563" t="s">
         <v>109</v>
       </c>
-      <c r="D26" s="605"/>
+      <c r="D26" s="563"/>
       <c r="E26" s="77"/>
       <c r="F26" s="78">
         <v>120</v>
@@ -24184,10 +24185,10 @@
       <c r="L26" s="80" t="s">
         <v>111</v>
       </c>
-      <c r="M26" s="543" t="s">
+      <c r="M26" s="564" t="s">
         <v>112</v>
       </c>
-      <c r="N26" s="544"/>
+      <c r="N26" s="565"/>
       <c r="O26" s="81"/>
       <c r="P26" s="82">
         <v>36</v>
@@ -24303,10 +24304,10 @@
       <c r="B27" s="158">
         <v>4</v>
       </c>
-      <c r="C27" s="605" t="s">
+      <c r="C27" s="563" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="605"/>
+      <c r="D27" s="563"/>
       <c r="E27" s="77"/>
       <c r="F27" s="78">
         <v>120</v>
@@ -24331,10 +24332,10 @@
       <c r="L27" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="M27" s="543" t="s">
+      <c r="M27" s="564" t="s">
         <v>88</v>
       </c>
-      <c r="N27" s="544"/>
+      <c r="N27" s="565"/>
       <c r="O27" s="81"/>
       <c r="P27" s="82">
         <v>46</v>
@@ -24507,36 +24508,36 @@
       <c r="J29" s="151"/>
     </row>
     <row r="30" spans="1:59" ht="24.75" customHeight="1" thickBot="1">
-      <c r="B30" s="537" t="s">
+      <c r="B30" s="560" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="538"/>
-      <c r="D30" s="538"/>
-      <c r="E30" s="538"/>
-      <c r="F30" s="538"/>
-      <c r="G30" s="538"/>
-      <c r="H30" s="538"/>
-      <c r="I30" s="538"/>
-      <c r="J30" s="539"/>
-      <c r="L30" s="602" t="s">
+      <c r="C30" s="561"/>
+      <c r="D30" s="561"/>
+      <c r="E30" s="561"/>
+      <c r="F30" s="561"/>
+      <c r="G30" s="561"/>
+      <c r="H30" s="561"/>
+      <c r="I30" s="561"/>
+      <c r="J30" s="562"/>
+      <c r="L30" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="M30" s="603"/>
-      <c r="N30" s="603"/>
-      <c r="O30" s="603"/>
-      <c r="P30" s="603"/>
-      <c r="Q30" s="603"/>
-      <c r="R30" s="603"/>
-      <c r="S30" s="603"/>
-      <c r="T30" s="603"/>
-      <c r="U30" s="603"/>
-      <c r="V30" s="603"/>
-      <c r="W30" s="603"/>
-      <c r="X30" s="603"/>
-      <c r="Y30" s="603"/>
-      <c r="Z30" s="603"/>
-      <c r="AA30" s="603"/>
-      <c r="AB30" s="604"/>
+      <c r="M30" s="555"/>
+      <c r="N30" s="555"/>
+      <c r="O30" s="555"/>
+      <c r="P30" s="555"/>
+      <c r="Q30" s="555"/>
+      <c r="R30" s="555"/>
+      <c r="S30" s="555"/>
+      <c r="T30" s="555"/>
+      <c r="U30" s="555"/>
+      <c r="V30" s="555"/>
+      <c r="W30" s="555"/>
+      <c r="X30" s="555"/>
+      <c r="Y30" s="555"/>
+      <c r="Z30" s="555"/>
+      <c r="AA30" s="555"/>
+      <c r="AB30" s="556"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
@@ -24659,10 +24660,10 @@
       <c r="B32" s="101">
         <v>1</v>
       </c>
-      <c r="C32" s="612" t="s">
+      <c r="C32" s="578" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="612"/>
+      <c r="D32" s="578"/>
       <c r="E32" s="102"/>
       <c r="F32" s="103">
         <v>120</v>
@@ -24684,10 +24685,10 @@
       <c r="L32" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="M32" s="610" t="s">
+      <c r="M32" s="567" t="s">
         <v>103</v>
       </c>
-      <c r="N32" s="611"/>
+      <c r="N32" s="568"/>
       <c r="O32" s="25"/>
       <c r="P32" s="26">
         <v>8</v>
@@ -24816,10 +24817,10 @@
       <c r="B33" s="51">
         <v>2</v>
       </c>
-      <c r="C33" s="613" t="s">
+      <c r="C33" s="569" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="613"/>
+      <c r="D33" s="569"/>
       <c r="E33" s="52"/>
       <c r="F33" s="53">
         <v>120</v>
@@ -24841,10 +24842,10 @@
       <c r="L33" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="M33" s="608" t="s">
+      <c r="M33" s="570" t="s">
         <v>107</v>
       </c>
-      <c r="N33" s="609"/>
+      <c r="N33" s="571"/>
       <c r="P33" s="58">
         <v>40</v>
       </c>
@@ -24960,10 +24961,10 @@
       <c r="B34" s="76">
         <v>3</v>
       </c>
-      <c r="C34" s="605" t="s">
+      <c r="C34" s="563" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="605"/>
+      <c r="D34" s="563"/>
       <c r="E34" s="77"/>
       <c r="F34" s="78">
         <v>120</v>
@@ -24985,10 +24986,10 @@
       <c r="L34" s="80" t="s">
         <v>111</v>
       </c>
-      <c r="M34" s="543" t="s">
+      <c r="M34" s="564" t="s">
         <v>112</v>
       </c>
-      <c r="N34" s="544"/>
+      <c r="N34" s="565"/>
       <c r="O34" s="81"/>
       <c r="P34" s="82">
         <v>37.5</v>
@@ -25104,10 +25105,10 @@
       <c r="B35" s="108">
         <v>4</v>
       </c>
-      <c r="C35" s="601" t="s">
+      <c r="C35" s="577" t="s">
         <v>85</v>
       </c>
-      <c r="D35" s="601"/>
+      <c r="D35" s="577"/>
       <c r="E35" s="109"/>
       <c r="F35" s="110">
         <v>120</v>
@@ -25129,10 +25130,10 @@
       <c r="L35" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="M35" s="543" t="s">
+      <c r="M35" s="564" t="s">
         <v>88</v>
       </c>
-      <c r="N35" s="544"/>
+      <c r="N35" s="565"/>
       <c r="O35" s="81"/>
       <c r="P35" s="82">
         <f>58/1.15</f>
@@ -25249,6 +25250,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="L15:AB15"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="L8:AB8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="M34:N34"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="L3:AB3"/>
     <mergeCell ref="M5:O5"/>
@@ -25265,45 +25305,6 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="N17:O17"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="L8:AB8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="L15:AB15"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25316,7 +25317,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:DS18"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
     <col min="2" max="2" width="4.28515625" customWidth="1"/>
@@ -25355,39 +25356,39 @@
   <sheetData>
     <row r="1" spans="1:123" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:123" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B2" s="619" t="s">
+      <c r="B2" s="597" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="620"/>
-      <c r="D2" s="620"/>
-      <c r="E2" s="620"/>
-      <c r="F2" s="620"/>
-      <c r="G2" s="620"/>
-      <c r="H2" s="620"/>
-      <c r="I2" s="620"/>
-      <c r="J2" s="621"/>
+      <c r="C2" s="598"/>
+      <c r="D2" s="598"/>
+      <c r="E2" s="598"/>
+      <c r="F2" s="598"/>
+      <c r="G2" s="598"/>
+      <c r="H2" s="598"/>
+      <c r="I2" s="598"/>
+      <c r="J2" s="599"/>
       <c r="K2" s="413" t="s">
         <v>119</v>
       </c>
-      <c r="L2" s="602" t="s">
+      <c r="L2" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="603"/>
-      <c r="N2" s="603"/>
-      <c r="O2" s="603"/>
-      <c r="P2" s="603"/>
-      <c r="Q2" s="603"/>
-      <c r="R2" s="603"/>
-      <c r="S2" s="603"/>
-      <c r="T2" s="603"/>
-      <c r="U2" s="603"/>
-      <c r="V2" s="603"/>
-      <c r="W2" s="603"/>
-      <c r="X2" s="603"/>
-      <c r="Y2" s="603"/>
-      <c r="Z2" s="603"/>
-      <c r="AA2" s="603"/>
-      <c r="AB2" s="604"/>
+      <c r="M2" s="555"/>
+      <c r="N2" s="555"/>
+      <c r="O2" s="555"/>
+      <c r="P2" s="555"/>
+      <c r="Q2" s="555"/>
+      <c r="R2" s="555"/>
+      <c r="S2" s="555"/>
+      <c r="T2" s="555"/>
+      <c r="U2" s="555"/>
+      <c r="V2" s="555"/>
+      <c r="W2" s="555"/>
+      <c r="X2" s="555"/>
+      <c r="Y2" s="555"/>
+      <c r="Z2" s="555"/>
+      <c r="AA2" s="555"/>
+      <c r="AB2" s="556"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
@@ -25509,10 +25510,10 @@
       <c r="B4" s="406">
         <v>1</v>
       </c>
-      <c r="C4" s="618" t="s">
+      <c r="C4" s="602" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="618"/>
+      <c r="D4" s="602"/>
       <c r="E4" s="407" t="s">
         <v>36</v>
       </c>
@@ -25538,11 +25539,11 @@
       <c r="L4" s="257" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="563" t="s">
+      <c r="M4" s="543" t="s">
         <v>124</v>
       </c>
-      <c r="N4" s="564"/>
-      <c r="O4" s="565"/>
+      <c r="N4" s="544"/>
+      <c r="O4" s="545"/>
       <c r="P4" s="258">
         <f>(78+((10*14)/164))/1.16</f>
         <v>67.97729184188394</v>
@@ -25668,37 +25669,37 @@
       <c r="L6"/>
     </row>
     <row r="7" spans="1:123" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B7" s="623" t="s">
+      <c r="B7" s="604" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="624"/>
-      <c r="D7" s="624"/>
-      <c r="E7" s="624"/>
-      <c r="F7" s="624"/>
-      <c r="G7" s="624"/>
-      <c r="H7" s="624"/>
-      <c r="I7" s="624"/>
-      <c r="J7" s="625"/>
+      <c r="C7" s="605"/>
+      <c r="D7" s="605"/>
+      <c r="E7" s="605"/>
+      <c r="F7" s="605"/>
+      <c r="G7" s="605"/>
+      <c r="H7" s="605"/>
+      <c r="I7" s="605"/>
+      <c r="J7" s="606"/>
       <c r="K7" s="255"/>
-      <c r="L7" s="602" t="s">
+      <c r="L7" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="M7" s="603"/>
-      <c r="N7" s="603"/>
-      <c r="O7" s="603"/>
-      <c r="P7" s="603"/>
-      <c r="Q7" s="603"/>
-      <c r="R7" s="603"/>
-      <c r="S7" s="603"/>
-      <c r="T7" s="603"/>
-      <c r="U7" s="603"/>
-      <c r="V7" s="603"/>
-      <c r="W7" s="603"/>
-      <c r="X7" s="603"/>
-      <c r="Y7" s="603"/>
-      <c r="Z7" s="603"/>
-      <c r="AA7" s="603"/>
-      <c r="AB7" s="604"/>
+      <c r="M7" s="555"/>
+      <c r="N7" s="555"/>
+      <c r="O7" s="555"/>
+      <c r="P7" s="555"/>
+      <c r="Q7" s="555"/>
+      <c r="R7" s="555"/>
+      <c r="S7" s="555"/>
+      <c r="T7" s="555"/>
+      <c r="U7" s="555"/>
+      <c r="V7" s="555"/>
+      <c r="W7" s="555"/>
+      <c r="X7" s="555"/>
+      <c r="Y7" s="555"/>
+      <c r="Z7" s="555"/>
+      <c r="AA7" s="555"/>
+      <c r="AB7" s="556"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
@@ -25821,10 +25822,10 @@
       <c r="B9" s="350">
         <v>1</v>
       </c>
-      <c r="C9" s="606" t="s">
+      <c r="C9" s="579" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="606"/>
+      <c r="D9" s="579"/>
       <c r="E9" s="342" t="s">
         <v>74</v>
       </c>
@@ -25847,14 +25848,14 @@
       <c r="K9" s="346">
         <v>32.590000000000003</v>
       </c>
-      <c r="L9" s="580" t="s">
+      <c r="L9" s="573" t="s">
         <v>77</v>
       </c>
-      <c r="M9" s="581"/>
-      <c r="N9" s="582" t="s">
+      <c r="M9" s="574"/>
+      <c r="N9" s="575" t="s">
         <v>78</v>
       </c>
-      <c r="O9" s="583"/>
+      <c r="O9" s="576"/>
       <c r="P9" s="166">
         <f>26.9/1.16</f>
         <v>23.189655172413794</v>
@@ -25955,10 +25956,10 @@
       <c r="B10" s="348">
         <v>2</v>
       </c>
-      <c r="C10" s="579" t="s">
+      <c r="C10" s="572" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="579"/>
+      <c r="D10" s="572"/>
       <c r="E10" s="343" t="s">
         <v>74</v>
       </c>
@@ -25981,14 +25982,14 @@
       <c r="K10" s="347">
         <v>41.5</v>
       </c>
-      <c r="L10" s="580" t="s">
+      <c r="L10" s="573" t="s">
         <v>81</v>
       </c>
-      <c r="M10" s="581"/>
-      <c r="N10" s="582" t="s">
+      <c r="M10" s="574"/>
+      <c r="N10" s="575" t="s">
         <v>82</v>
       </c>
-      <c r="O10" s="583"/>
+      <c r="O10" s="576"/>
       <c r="P10" s="166">
         <f>34.5/1.16</f>
         <v>29.741379310344829</v>
@@ -26089,10 +26090,10 @@
       <c r="B11" s="353">
         <v>3</v>
       </c>
-      <c r="C11" s="622" t="s">
+      <c r="C11" s="603" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="622"/>
+      <c r="D11" s="603"/>
       <c r="E11" s="337" t="s">
         <v>130</v>
       </c>
@@ -26117,10 +26118,10 @@
         <v>133</v>
       </c>
       <c r="M11" s="320"/>
-      <c r="N11" s="540" t="s">
+      <c r="N11" s="607" t="s">
         <v>134</v>
       </c>
-      <c r="O11" s="541"/>
+      <c r="O11" s="608"/>
       <c r="P11" s="321">
         <v>22</v>
       </c>
@@ -26198,37 +26199,37 @@
     </row>
     <row r="12" spans="1:123" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:123" ht="40.5" customHeight="1" thickBot="1">
-      <c r="B13" s="619" t="s">
+      <c r="B13" s="597" t="s">
         <v>136</v>
       </c>
-      <c r="C13" s="620"/>
-      <c r="D13" s="620"/>
-      <c r="E13" s="620"/>
-      <c r="F13" s="620"/>
-      <c r="G13" s="620"/>
-      <c r="H13" s="620"/>
-      <c r="I13" s="620"/>
-      <c r="J13" s="621"/>
+      <c r="C13" s="598"/>
+      <c r="D13" s="598"/>
+      <c r="E13" s="598"/>
+      <c r="F13" s="598"/>
+      <c r="G13" s="598"/>
+      <c r="H13" s="598"/>
+      <c r="I13" s="598"/>
+      <c r="J13" s="599"/>
       <c r="K13" s="255"/>
-      <c r="L13" s="602" t="s">
+      <c r="L13" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="603"/>
-      <c r="N13" s="603"/>
-      <c r="O13" s="603"/>
-      <c r="P13" s="603"/>
-      <c r="Q13" s="603"/>
-      <c r="R13" s="603"/>
-      <c r="S13" s="603"/>
-      <c r="T13" s="603"/>
-      <c r="U13" s="603"/>
-      <c r="V13" s="603"/>
-      <c r="W13" s="603"/>
-      <c r="X13" s="603"/>
-      <c r="Y13" s="603"/>
-      <c r="Z13" s="603"/>
-      <c r="AA13" s="603"/>
-      <c r="AB13" s="604"/>
+      <c r="M13" s="555"/>
+      <c r="N13" s="555"/>
+      <c r="O13" s="555"/>
+      <c r="P13" s="555"/>
+      <c r="Q13" s="555"/>
+      <c r="R13" s="555"/>
+      <c r="S13" s="555"/>
+      <c r="T13" s="555"/>
+      <c r="U13" s="555"/>
+      <c r="V13" s="555"/>
+      <c r="W13" s="555"/>
+      <c r="X13" s="555"/>
+      <c r="Y13" s="555"/>
+      <c r="Z13" s="555"/>
+      <c r="AA13" s="555"/>
+      <c r="AB13" s="556"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
       <c r="AE13" s="1"/>
@@ -26351,10 +26352,10 @@
       <c r="B15" s="309">
         <v>1</v>
       </c>
-      <c r="C15" s="626" t="s">
+      <c r="C15" s="600" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="626"/>
+      <c r="D15" s="600"/>
       <c r="E15" s="301" t="s">
         <v>36</v>
       </c>
@@ -26381,11 +26382,11 @@
       <c r="L15" s="279" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="566" t="s">
+      <c r="M15" s="548" t="s">
         <v>139</v>
       </c>
-      <c r="N15" s="567"/>
-      <c r="O15" s="568"/>
+      <c r="N15" s="549"/>
+      <c r="O15" s="550"/>
       <c r="P15" s="280">
         <v>58.5</v>
       </c>
@@ -26576,10 +26577,10 @@
       <c r="B16" s="311">
         <v>2</v>
       </c>
-      <c r="C16" s="627" t="s">
+      <c r="C16" s="601" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="627"/>
+      <c r="D16" s="601"/>
       <c r="E16" s="312" t="s">
         <v>36</v>
       </c>
@@ -26606,11 +26607,11 @@
       <c r="L16" s="257" t="s">
         <v>39</v>
       </c>
-      <c r="M16" s="563" t="s">
+      <c r="M16" s="543" t="s">
         <v>141</v>
       </c>
-      <c r="N16" s="564"/>
-      <c r="O16" s="565"/>
+      <c r="N16" s="544"/>
+      <c r="O16" s="545"/>
       <c r="P16" s="258">
         <f>78/1.18</f>
         <v>66.101694915254242</v>
@@ -26706,12 +26707,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="L13:AB13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="M16:O16"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="M4:O4"/>
     <mergeCell ref="B2:J2"/>
@@ -26726,6 +26721,12 @@
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="L13:AB13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="M16:O16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -26736,7 +26737,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AJ3"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="424" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" style="424" customWidth="1"/>
@@ -26780,17 +26781,17 @@
   <sheetData>
     <row r="1" spans="1:36" s="419" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
       <c r="A1" s="414"/>
-      <c r="B1" s="537" t="s">
+      <c r="B1" s="560" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="538"/>
-      <c r="D1" s="538"/>
-      <c r="E1" s="538"/>
-      <c r="F1" s="538"/>
-      <c r="G1" s="538"/>
-      <c r="H1" s="538"/>
-      <c r="I1" s="538"/>
-      <c r="J1" s="539"/>
+      <c r="C1" s="561"/>
+      <c r="D1" s="561"/>
+      <c r="E1" s="561"/>
+      <c r="F1" s="561"/>
+      <c r="G1" s="561"/>
+      <c r="H1" s="561"/>
+      <c r="I1" s="561"/>
+      <c r="J1" s="562"/>
       <c r="K1" s="415"/>
       <c r="L1" s="415"/>
       <c r="M1" s="416"/>
@@ -26935,10 +26936,10 @@
       <c r="B3" s="448">
         <v>1</v>
       </c>
-      <c r="C3" s="628" t="s">
+      <c r="C3" s="609" t="s">
         <v>150</v>
       </c>
-      <c r="D3" s="629"/>
+      <c r="D3" s="610"/>
       <c r="E3" s="449"/>
       <c r="F3" s="450">
         <v>100</v>
@@ -26960,11 +26961,11 @@
       <c r="L3" s="427" t="s">
         <v>153</v>
       </c>
-      <c r="M3" s="630" t="s">
+      <c r="M3" s="611" t="s">
         <v>154</v>
       </c>
-      <c r="N3" s="631"/>
-      <c r="O3" s="632"/>
+      <c r="N3" s="612"/>
+      <c r="O3" s="613"/>
       <c r="P3" s="428">
         <v>10.5</v>
       </c>
@@ -27056,7 +27057,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:IV9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="5.42578125" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" customWidth="1"/>
@@ -27084,17 +27085,17 @@
   <sheetData>
     <row r="1" spans="1:256" s="419" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
       <c r="A1" s="414"/>
-      <c r="B1" s="537" t="s">
+      <c r="B1" s="560" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="538"/>
-      <c r="D1" s="538"/>
-      <c r="E1" s="538"/>
-      <c r="F1" s="538"/>
-      <c r="G1" s="538"/>
-      <c r="H1" s="538"/>
-      <c r="I1" s="538"/>
-      <c r="J1" s="539"/>
+      <c r="C1" s="561"/>
+      <c r="D1" s="561"/>
+      <c r="E1" s="561"/>
+      <c r="F1" s="561"/>
+      <c r="G1" s="561"/>
+      <c r="H1" s="561"/>
+      <c r="I1" s="561"/>
+      <c r="J1" s="562"/>
       <c r="K1" s="415"/>
       <c r="L1" s="415"/>
       <c r="M1" s="416"/>
@@ -27237,10 +27238,10 @@
       <c r="B3" s="504">
         <v>1</v>
       </c>
-      <c r="C3" s="533" t="s">
+      <c r="C3" s="631" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="533"/>
+      <c r="D3" s="631"/>
       <c r="E3" s="505"/>
       <c r="F3" s="506">
         <v>178</v>
@@ -27263,11 +27264,11 @@
       <c r="L3" s="511" t="s">
         <v>160</v>
       </c>
-      <c r="M3" s="534" t="s">
+      <c r="M3" s="632" t="s">
         <v>161</v>
       </c>
-      <c r="N3" s="535"/>
-      <c r="O3" s="536"/>
+      <c r="N3" s="633"/>
+      <c r="O3" s="634"/>
       <c r="P3" s="512">
         <f>65+10</f>
         <v>75</v>
@@ -27591,17 +27592,17 @@
     <row r="4" spans="1:256" ht="15.75" thickBot="1"/>
     <row r="5" spans="1:256" s="419" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
       <c r="A5" s="414"/>
-      <c r="B5" s="537" t="s">
+      <c r="B5" s="560" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="538"/>
-      <c r="D5" s="538"/>
-      <c r="E5" s="538"/>
-      <c r="F5" s="538"/>
-      <c r="G5" s="538"/>
-      <c r="H5" s="538"/>
-      <c r="I5" s="538"/>
-      <c r="J5" s="539"/>
+      <c r="C5" s="561"/>
+      <c r="D5" s="561"/>
+      <c r="E5" s="561"/>
+      <c r="F5" s="561"/>
+      <c r="G5" s="561"/>
+      <c r="H5" s="561"/>
+      <c r="I5" s="561"/>
+      <c r="J5" s="562"/>
       <c r="K5" s="415"/>
       <c r="L5" s="415"/>
       <c r="M5" s="416"/>
@@ -27741,30 +27742,30 @@
     </row>
     <row r="7" spans="1:256" s="424" customFormat="1" ht="69" customHeight="1">
       <c r="A7" s="420"/>
-      <c r="B7" s="549">
+      <c r="B7" s="619">
         <v>1</v>
       </c>
-      <c r="C7" s="547" t="s">
+      <c r="C7" s="617" t="s">
         <v>163</v>
       </c>
-      <c r="D7" s="547"/>
-      <c r="E7" s="545" t="s">
+      <c r="D7" s="617"/>
+      <c r="E7" s="615" t="s">
         <v>130</v>
       </c>
-      <c r="F7" s="559">
+      <c r="F7" s="629">
         <v>178</v>
       </c>
-      <c r="G7" s="557">
+      <c r="G7" s="627">
         <f>AH8</f>
         <v>228.63467696629215</v>
       </c>
-      <c r="H7" s="555" t="s">
+      <c r="H7" s="625" t="s">
         <v>131</v>
       </c>
-      <c r="I7" s="553" t="s">
+      <c r="I7" s="623" t="s">
         <v>164</v>
       </c>
-      <c r="J7" s="551">
+      <c r="J7" s="621">
         <f>F7*G7</f>
         <v>40696.972500000003</v>
       </c>
@@ -27797,15 +27798,15 @@
     </row>
     <row r="8" spans="1:256" s="318" customFormat="1" ht="409.5" customHeight="1" thickBot="1">
       <c r="A8" s="483"/>
-      <c r="B8" s="550"/>
-      <c r="C8" s="548"/>
-      <c r="D8" s="548"/>
-      <c r="E8" s="546"/>
-      <c r="F8" s="560"/>
-      <c r="G8" s="558"/>
-      <c r="H8" s="556"/>
-      <c r="I8" s="554"/>
-      <c r="J8" s="552"/>
+      <c r="B8" s="620"/>
+      <c r="C8" s="618"/>
+      <c r="D8" s="618"/>
+      <c r="E8" s="616"/>
+      <c r="F8" s="630"/>
+      <c r="G8" s="628"/>
+      <c r="H8" s="626"/>
+      <c r="I8" s="624"/>
+      <c r="J8" s="622"/>
       <c r="K8" s="319"/>
       <c r="L8" s="320" t="s">
         <v>165</v>
@@ -27813,10 +27814,10 @@
       <c r="M8" s="458" t="s">
         <v>166</v>
       </c>
-      <c r="N8" s="540" t="s">
+      <c r="N8" s="607" t="s">
         <v>167</v>
       </c>
-      <c r="O8" s="541"/>
+      <c r="O8" s="608"/>
       <c r="P8" s="321">
         <f>(207/1.15)+0.2</f>
         <v>180.2</v>
@@ -27899,10 +27900,10 @@
       <c r="B9" s="487">
         <v>2</v>
       </c>
-      <c r="C9" s="542" t="s">
+      <c r="C9" s="614" t="s">
         <v>169</v>
       </c>
-      <c r="D9" s="542"/>
+      <c r="D9" s="614"/>
       <c r="E9" s="337" t="s">
         <v>130</v>
       </c>
@@ -27927,10 +27928,10 @@
         <v>133</v>
       </c>
       <c r="M9" s="460"/>
-      <c r="N9" s="543" t="s">
+      <c r="N9" s="564" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="544"/>
+      <c r="O9" s="565"/>
       <c r="P9" s="321">
         <f>70/1.15</f>
         <v>60.869565217391312</v>
@@ -28011,6 +28012,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="N8:O8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="N9:O9"/>
     <mergeCell ref="E7:E8"/>
@@ -28021,11 +28027,6 @@
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="N8:O8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="M8" r:id="rId1" location="/32-color-negro" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
